--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B911424-E516-45E9-B1B5-0B828FE6F83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C16D11EB-1E14-4569-9BCA-3353B2B1B2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ECD9FD24-4B9B-4EF2-827D-F289F3A90AF2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{33A2BFEE-FD46-499B-90CE-B59041106899}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6489C498-CE33-4AA9-A236-036BC35FA977}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BF6FC5-6A53-4B82-9200-25C0338032BE}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E769C5A-6FD5-47C2-87A2-00FA893899DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C35BFDF-804B-4CE6-9E01-AA7B3EBADF47}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC552880-B438-4FC1-9096-57C4E865E0CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57132A9D-289D-4FC8-9385-53EBA25459C0}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19954,7 +19954,7 @@
         <v>33</v>
       </c>
       <c r="L119">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N119" t="s">
         <v>176</v>
@@ -20001,7 +20001,7 @@
         <v>33</v>
       </c>
       <c r="L120">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N120" t="s">
         <v>176</v>
@@ -20048,7 +20048,7 @@
         <v>33</v>
       </c>
       <c r="L121">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N121" t="s">
         <v>176</v>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{370E1A42-54A9-4404-93F1-B703A42BB756}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5D8A99-C2DC-4A3A-8FB9-27134FB9E32C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C16D11EB-1E14-4569-9BCA-3353B2B1B2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0894848-FAD6-43D8-B288-13F65A1883AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{33A2BFEE-FD46-499B-90CE-B59041106899}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{288FFCCD-AC1B-482D-A94F-486E6B32BA80}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BF6FC5-6A53-4B82-9200-25C0338032BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534918F1-0839-40A6-B370-04213854E44D}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C35BFDF-804B-4CE6-9E01-AA7B3EBADF47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978721DE-5559-4512-AB04-0C9C84EBB872}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57132A9D-289D-4FC8-9385-53EBA25459C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6434C1-045E-4C00-B92C-01D4DEB88D80}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19954,7 +19954,7 @@
         <v>33</v>
       </c>
       <c r="L119">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N119" t="s">
         <v>176</v>
@@ -20001,7 +20001,7 @@
         <v>33</v>
       </c>
       <c r="L120">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N120" t="s">
         <v>176</v>
@@ -20048,7 +20048,7 @@
         <v>33</v>
       </c>
       <c r="L121">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N121" t="s">
         <v>176</v>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5D8A99-C2DC-4A3A-8FB9-27134FB9E32C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214470C-EE7A-48A5-9A60-D8229F77E492}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0894848-FAD6-43D8-B288-13F65A1883AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE57B8D-5151-4A9F-A325-DBCC1FB76BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{288FFCCD-AC1B-482D-A94F-486E6B32BA80}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6C8174D9-A5D4-4A07-A1E9-D4E3CFA54938}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534918F1-0839-40A6-B370-04213854E44D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256C5FCE-2206-4387-A26A-46FE50D2AB9D}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978721DE-5559-4512-AB04-0C9C84EBB872}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E94946-32D7-4E6E-8BAB-EA57CD5D2BB6}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6434C1-045E-4C00-B92C-01D4DEB88D80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B72006-261C-491B-ADCD-36FB4F1EBA73}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19954,7 +19954,7 @@
         <v>33</v>
       </c>
       <c r="L119">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N119" t="s">
         <v>176</v>
@@ -20001,7 +20001,7 @@
         <v>33</v>
       </c>
       <c r="L120">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N120" t="s">
         <v>176</v>
@@ -20048,7 +20048,7 @@
         <v>33</v>
       </c>
       <c r="L121">
-        <v>0.2131212374931396</v>
+        <v>0.21312123749313963</v>
       </c>
       <c r="N121" t="s">
         <v>176</v>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214470C-EE7A-48A5-9A60-D8229F77E492}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DD1A99-B047-43BB-A925-BEF56EDD7536}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE57B8D-5151-4A9F-A325-DBCC1FB76BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B4237A5-2E54-4F19-8FD2-C332928192F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6C8174D9-A5D4-4A07-A1E9-D4E3CFA54938}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1997B431-4713-4B14-B48C-FCCCC22C633C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256C5FCE-2206-4387-A26A-46FE50D2AB9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E37BD2-E130-4990-B816-E585A6A49600}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E94946-32D7-4E6E-8BAB-EA57CD5D2BB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DC6DC5-ED76-4B9C-BE26-6BBC74061199}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B72006-261C-491B-ADCD-36FB4F1EBA73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28565C-F466-4610-B9C6-B65EE4894314}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19954,7 +19954,7 @@
         <v>33</v>
       </c>
       <c r="L119">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N119" t="s">
         <v>176</v>
@@ -20001,7 +20001,7 @@
         <v>33</v>
       </c>
       <c r="L120">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N120" t="s">
         <v>176</v>
@@ -20048,7 +20048,7 @@
         <v>33</v>
       </c>
       <c r="L121">
-        <v>0.21312123749313963</v>
+        <v>0.2131212374931396</v>
       </c>
       <c r="N121" t="s">
         <v>176</v>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DD1A99-B047-43BB-A925-BEF56EDD7536}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D28393A8-4D47-49FA-8472-659AB175D14E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B4237A5-2E54-4F19-8FD2-C332928192F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D85304-2965-4BE9-9183-854EF7CA585C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1997B431-4713-4B14-B48C-FCCCC22C633C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6AFA396B-B6EB-4900-BF57-366F30FE1C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E37BD2-E130-4990-B816-E585A6A49600}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA298E2-60A4-4622-BC37-0D7F387C1CB8}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DC6DC5-ED76-4B9C-BE26-6BBC74061199}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B339189-D56E-487F-96B2-8E837A0269FC}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28565C-F466-4610-B9C6-B65EE4894314}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2BE32C3-702A-4ECB-AB90-8214BC552891}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D28393A8-4D47-49FA-8472-659AB175D14E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26C88B5-6581-41E9-A29D-ABF850D730BD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D85304-2965-4BE9-9183-854EF7CA585C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BA999F7-57B3-45E1-8B20-CC2D1A790883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6AFA396B-B6EB-4900-BF57-366F30FE1C6C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{292A7CD7-1373-4722-B2AC-C766CDC80DF5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA298E2-60A4-4622-BC37-0D7F387C1CB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04B2776-32CB-495A-B040-C3E2FDFD55E6}">
   <dimension ref="B9:T111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8311,7 +8311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B339189-D56E-487F-96B2-8E837A0269FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5DBBB3-CBCE-4398-977D-11017921E913}">
   <dimension ref="B9:T118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14148,7 +14148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2BE32C3-702A-4ECB-AB90-8214BC552891}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CBAAFB-D810-492E-85A6-46B85F8B4EC2}">
   <dimension ref="B9:T129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20505,7 +20505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26C88B5-6581-41E9-A29D-ABF850D730BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439D1BC7-1E5D-4807-AE36-D0760B54252C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
